--- a/artfynd/A 40936-2024 artfynd.xlsx
+++ b/artfynd/A 40936-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120978062</v>
+        <v>120978060</v>
       </c>
       <c r="B2" t="n">
-        <v>78598</v>
+        <v>77545</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543075</v>
+        <v>543079</v>
       </c>
       <c r="R2" t="n">
-        <v>7209164</v>
+        <v>7209176</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120978060</v>
+        <v>120978036</v>
       </c>
       <c r="B3" t="n">
-        <v>77545</v>
+        <v>57348</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>314</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543079</v>
+        <v>543123</v>
       </c>
       <c r="R3" t="n">
-        <v>7209176</v>
+        <v>7209054</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120978035</v>
+        <v>120978006</v>
       </c>
       <c r="B4" t="n">
-        <v>78598</v>
+        <v>57348</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,34 +920,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543116</v>
+        <v>543075</v>
       </c>
       <c r="R4" t="n">
-        <v>7209226</v>
+        <v>7209798</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +994,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Påbörjat bohål</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,7 +1026,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120978036</v>
+        <v>120978034</v>
       </c>
       <c r="B5" t="n">
         <v>57348</v>
@@ -1047,7 +1062,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1056,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543123</v>
+        <v>543114</v>
       </c>
       <c r="R5" t="n">
-        <v>7209054</v>
+        <v>7209229</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1106,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1116,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120978006</v>
+        <v>120978062</v>
       </c>
       <c r="B6" t="n">
-        <v>57348</v>
+        <v>78598</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,29 +1159,24 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
@@ -1176,7 +1186,7 @@
         <v>543075</v>
       </c>
       <c r="R6" t="n">
-        <v>7209798</v>
+        <v>7209164</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,12 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:37</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Påbörjat bohål</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120978034</v>
+        <v>120978035</v>
       </c>
       <c r="B7" t="n">
-        <v>57348</v>
+        <v>78598</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,39 +1271,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543114</v>
+        <v>543116</v>
       </c>
       <c r="R7" t="n">
-        <v>7209229</v>
+        <v>7209226</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1819,7 +1819,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120978048</v>
+        <v>120978052</v>
       </c>
       <c r="B12" t="n">
         <v>78598</v>
@@ -1859,10 +1859,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>543107</v>
+        <v>543096</v>
       </c>
       <c r="R12" t="n">
-        <v>7209000</v>
+        <v>7209059</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1894,7 +1894,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1931,10 +1931,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120978040</v>
+        <v>120978056</v>
       </c>
       <c r="B13" t="n">
-        <v>78598</v>
+        <v>90705</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1947,21 +1947,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>543164</v>
+        <v>543091</v>
       </c>
       <c r="R13" t="n">
-        <v>7208974</v>
+        <v>7209092</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2043,7 +2043,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120978052</v>
+        <v>120978048</v>
       </c>
       <c r="B14" t="n">
         <v>78598</v>
@@ -2083,10 +2083,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>543096</v>
+        <v>543107</v>
       </c>
       <c r="R14" t="n">
-        <v>7209059</v>
+        <v>7209000</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2155,10 +2155,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120978056</v>
+        <v>120978040</v>
       </c>
       <c r="B15" t="n">
-        <v>90705</v>
+        <v>78598</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2171,21 +2171,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2195,10 +2195,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>543091</v>
+        <v>543164</v>
       </c>
       <c r="R15" t="n">
-        <v>7209092</v>
+        <v>7208974</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2230,7 +2230,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2240,7 +2240,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2491,10 +2491,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120978013</v>
+        <v>120978032</v>
       </c>
       <c r="B18" t="n">
-        <v>79714</v>
+        <v>57348</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2503,38 +2503,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>543076</v>
+        <v>543135</v>
       </c>
       <c r="R18" t="n">
-        <v>7209851</v>
+        <v>7209257</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2566,7 +2571,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2576,7 +2581,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2603,7 +2608,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120978032</v>
+        <v>120977997</v>
       </c>
       <c r="B19" t="n">
         <v>57348</v>
@@ -2648,10 +2653,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>543135</v>
+        <v>543057</v>
       </c>
       <c r="R19" t="n">
-        <v>7209257</v>
+        <v>7209403</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2683,7 +2688,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2693,7 +2698,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2720,10 +2725,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120977997</v>
+        <v>120978020</v>
       </c>
       <c r="B20" t="n">
-        <v>57348</v>
+        <v>57459</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2732,20 +2737,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2753,10 +2758,9 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2765,10 +2769,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>543057</v>
+        <v>543115</v>
       </c>
       <c r="R20" t="n">
-        <v>7209403</v>
+        <v>7209734</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2800,7 +2804,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2810,7 +2814,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2837,10 +2841,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120978020</v>
+        <v>120978013</v>
       </c>
       <c r="B21" t="n">
-        <v>57459</v>
+        <v>79714</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2853,38 +2857,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103031</v>
+        <v>6463</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>543115</v>
+        <v>543076</v>
       </c>
       <c r="R21" t="n">
-        <v>7209734</v>
+        <v>7209851</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -6922,10 +6922,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120978049</v>
+        <v>120978050</v>
       </c>
       <c r="B57" t="n">
-        <v>90683</v>
+        <v>78598</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6938,21 +6938,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6962,10 +6962,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>543099</v>
+        <v>543101</v>
       </c>
       <c r="R57" t="n">
-        <v>7209028</v>
+        <v>7209025</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -7034,10 +7034,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120977999</v>
+        <v>120978049</v>
       </c>
       <c r="B58" t="n">
-        <v>78598</v>
+        <v>90683</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7050,21 +7050,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7074,10 +7074,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>543048</v>
+        <v>543099</v>
       </c>
       <c r="R58" t="n">
-        <v>7209511</v>
+        <v>7209028</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7109,7 +7109,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7119,7 +7119,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7380,7 +7380,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120978050</v>
+        <v>120977999</v>
       </c>
       <c r="B61" t="n">
         <v>78598</v>
@@ -7420,10 +7420,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>543101</v>
+        <v>543048</v>
       </c>
       <c r="R61" t="n">
-        <v>7209025</v>
+        <v>7209511</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7455,7 +7455,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7465,7 +7465,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 40936-2024 artfynd.xlsx
+++ b/artfynd/A 40936-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120978060</v>
+        <v>120978019</v>
       </c>
       <c r="B2" t="n">
-        <v>77545</v>
+        <v>79711</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>314</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543079</v>
+        <v>543161</v>
       </c>
       <c r="R2" t="n">
-        <v>7209176</v>
+        <v>7209834</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120978036</v>
+        <v>120978029</v>
       </c>
       <c r="B3" t="n">
-        <v>57348</v>
+        <v>78601</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543123</v>
+        <v>543068</v>
       </c>
       <c r="R3" t="n">
-        <v>7209054</v>
+        <v>7209436</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120978006</v>
+        <v>120978051</v>
       </c>
       <c r="B4" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -949,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543075</v>
+        <v>543095</v>
       </c>
       <c r="R4" t="n">
-        <v>7209798</v>
+        <v>7209049</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:37</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Påbörjat bohål</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120978034</v>
+        <v>120978042</v>
       </c>
       <c r="B5" t="n">
-        <v>57348</v>
+        <v>57462</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1038,20 +1028,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1059,10 +1049,9 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1071,10 +1060,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543114</v>
+        <v>543149</v>
       </c>
       <c r="R5" t="n">
-        <v>7209229</v>
+        <v>7208877</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1106,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1116,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120978062</v>
+        <v>120978009</v>
       </c>
       <c r="B6" t="n">
-        <v>78598</v>
+        <v>79682</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,21 +1148,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543075</v>
+        <v>543069</v>
       </c>
       <c r="R6" t="n">
-        <v>7209164</v>
+        <v>7209839</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1218,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120978035</v>
+        <v>120978038</v>
       </c>
       <c r="B7" t="n">
-        <v>78598</v>
+        <v>57351</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,34 +1260,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543116</v>
+        <v>543133</v>
       </c>
       <c r="R7" t="n">
-        <v>7209226</v>
+        <v>7209037</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1330,7 +1324,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1334,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120978030</v>
+        <v>120977996</v>
       </c>
       <c r="B8" t="n">
-        <v>57501</v>
+        <v>57351</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,26 +1377,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1411,10 +1406,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543137</v>
+        <v>543049</v>
       </c>
       <c r="R8" t="n">
-        <v>7209282</v>
+        <v>7209349</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1446,7 +1441,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1451,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1483,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120978023</v>
+        <v>120978049</v>
       </c>
       <c r="B9" t="n">
-        <v>90683</v>
+        <v>90693</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1523,10 +1518,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>543114</v>
+        <v>543099</v>
       </c>
       <c r="R9" t="n">
-        <v>7209734</v>
+        <v>7209028</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1558,7 +1553,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1568,7 +1563,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1598,7 +1593,7 @@
         <v>120978063</v>
       </c>
       <c r="B10" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1707,10 +1702,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120978059</v>
+        <v>120978008</v>
       </c>
       <c r="B11" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1747,10 +1742,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>543087</v>
+        <v>543067</v>
       </c>
       <c r="R11" t="n">
-        <v>7209098</v>
+        <v>7209836</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1782,7 +1777,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1792,7 +1787,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1819,10 +1814,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120978052</v>
+        <v>120978037</v>
       </c>
       <c r="B12" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1859,10 +1854,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>543096</v>
+        <v>543124</v>
       </c>
       <c r="R12" t="n">
-        <v>7209059</v>
+        <v>7209053</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1894,7 +1889,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1904,7 +1899,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1931,10 +1926,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120978056</v>
+        <v>120978039</v>
       </c>
       <c r="B13" t="n">
-        <v>90705</v>
+        <v>78601</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1947,21 +1942,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1971,10 +1966,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>543091</v>
+        <v>543134</v>
       </c>
       <c r="R13" t="n">
-        <v>7209092</v>
+        <v>7209039</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2006,7 +2001,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2016,7 +2011,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2043,10 +2038,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120978048</v>
+        <v>120978014</v>
       </c>
       <c r="B14" t="n">
-        <v>78598</v>
+        <v>57351</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2059,34 +2054,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>543107</v>
+        <v>543091</v>
       </c>
       <c r="R14" t="n">
-        <v>7209000</v>
+        <v>7209831</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2155,10 +2155,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120978040</v>
+        <v>120978026</v>
       </c>
       <c r="B15" t="n">
-        <v>78598</v>
+        <v>57351</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2171,34 +2171,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>543164</v>
+        <v>543114</v>
       </c>
       <c r="R15" t="n">
-        <v>7208974</v>
+        <v>7209471</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2230,7 +2235,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2240,7 +2245,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2267,10 +2272,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120978001</v>
+        <v>120978025</v>
       </c>
       <c r="B16" t="n">
-        <v>79680</v>
+        <v>78601</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2283,21 +2288,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2307,10 +2312,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>543045</v>
+        <v>543116</v>
       </c>
       <c r="R16" t="n">
-        <v>7209613</v>
+        <v>7209729</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2342,7 +2347,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2352,7 +2357,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2379,10 +2384,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120978025</v>
+        <v>120978010</v>
       </c>
       <c r="B17" t="n">
-        <v>78598</v>
+        <v>79711</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2391,25 +2396,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2419,10 +2424,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>543116</v>
+        <v>543067</v>
       </c>
       <c r="R17" t="n">
-        <v>7209729</v>
+        <v>7209836</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2454,7 +2459,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2464,7 +2469,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2491,10 +2496,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120978032</v>
+        <v>120978023</v>
       </c>
       <c r="B18" t="n">
-        <v>57348</v>
+        <v>90693</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2507,39 +2512,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>543135</v>
+        <v>543114</v>
       </c>
       <c r="R18" t="n">
-        <v>7209257</v>
+        <v>7209734</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2608,10 +2608,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120977997</v>
+        <v>120978003</v>
       </c>
       <c r="B19" t="n">
-        <v>57348</v>
+        <v>82385</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2624,39 +2624,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>543057</v>
+        <v>543045</v>
       </c>
       <c r="R19" t="n">
-        <v>7209403</v>
+        <v>7209634</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2688,7 +2683,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2698,7 +2693,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2725,10 +2720,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120978020</v>
+        <v>120978047</v>
       </c>
       <c r="B20" t="n">
-        <v>57459</v>
+        <v>90693</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2737,42 +2732,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103031</v>
+        <v>1108</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>543115</v>
+        <v>543105</v>
       </c>
       <c r="R20" t="n">
-        <v>7209734</v>
+        <v>7209001</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2804,7 +2795,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2814,7 +2805,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2841,10 +2832,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120978013</v>
+        <v>120978024</v>
       </c>
       <c r="B21" t="n">
-        <v>79714</v>
+        <v>91090</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2853,25 +2844,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6463</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Bårdlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2881,10 +2867,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>543076</v>
+        <v>543114</v>
       </c>
       <c r="R21" t="n">
-        <v>7209851</v>
+        <v>7209731</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2916,7 +2902,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2926,7 +2912,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2953,10 +2939,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120978024</v>
+        <v>120978028</v>
       </c>
       <c r="B22" t="n">
-        <v>91080</v>
+        <v>57351</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2969,29 +2955,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6040186</v>
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>543114</v>
+        <v>543068</v>
       </c>
       <c r="R22" t="n">
-        <v>7209731</v>
+        <v>7209436</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3023,7 +3019,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3033,7 +3029,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3060,10 +3056,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120978004</v>
+        <v>120978016</v>
       </c>
       <c r="B23" t="n">
-        <v>78598</v>
+        <v>79682</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3076,21 +3072,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3100,10 +3096,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>543044</v>
+        <v>543095</v>
       </c>
       <c r="R23" t="n">
-        <v>7209633</v>
+        <v>7209831</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3135,7 +3131,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3145,7 +3141,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3172,10 +3168,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120978027</v>
+        <v>120978059</v>
       </c>
       <c r="B24" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3212,10 +3208,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>543112</v>
+        <v>543087</v>
       </c>
       <c r="R24" t="n">
-        <v>7209467</v>
+        <v>7209098</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3247,7 +3243,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3257,7 +3253,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3284,10 +3280,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120978053</v>
+        <v>120978032</v>
       </c>
       <c r="B25" t="n">
-        <v>91080</v>
+        <v>57351</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3300,29 +3296,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6040186</v>
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>543105</v>
+        <v>543135</v>
       </c>
       <c r="R25" t="n">
-        <v>7209074</v>
+        <v>7209257</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3354,7 +3360,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3364,7 +3370,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3391,10 +3397,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120978042</v>
+        <v>120978045</v>
       </c>
       <c r="B26" t="n">
-        <v>57459</v>
+        <v>57351</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3403,20 +3409,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3424,9 +3430,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3435,10 +3442,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>543149</v>
+        <v>543114</v>
       </c>
       <c r="R26" t="n">
-        <v>7208877</v>
+        <v>7208935</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3470,7 +3477,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3480,7 +3487,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3507,10 +3514,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120978041</v>
+        <v>120978007</v>
       </c>
       <c r="B27" t="n">
-        <v>57348</v>
+        <v>79683</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3523,39 +3530,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>543164</v>
+        <v>543068</v>
       </c>
       <c r="R27" t="n">
-        <v>7208974</v>
+        <v>7209835</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3587,7 +3589,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3597,7 +3599,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3624,10 +3626,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120978055</v>
+        <v>120978033</v>
       </c>
       <c r="B28" t="n">
-        <v>57348</v>
+        <v>78601</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3640,39 +3642,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>543091</v>
+        <v>543133</v>
       </c>
       <c r="R28" t="n">
-        <v>7209093</v>
+        <v>7209253</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3704,7 +3701,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3714,7 +3711,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3741,10 +3738,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120978021</v>
+        <v>120978050</v>
       </c>
       <c r="B29" t="n">
-        <v>91042</v>
+        <v>78601</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3753,25 +3750,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1506</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3781,10 +3778,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>543115</v>
+        <v>543101</v>
       </c>
       <c r="R29" t="n">
-        <v>7209734</v>
+        <v>7209025</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3816,7 +3813,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3826,7 +3823,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3853,10 +3850,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120978016</v>
+        <v>120977997</v>
       </c>
       <c r="B30" t="n">
-        <v>79679</v>
+        <v>57351</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3869,34 +3866,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>543095</v>
+        <v>543057</v>
       </c>
       <c r="R30" t="n">
-        <v>7209831</v>
+        <v>7209403</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3928,7 +3930,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3938,7 +3940,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3965,10 +3967,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120978043</v>
+        <v>120978054</v>
       </c>
       <c r="B31" t="n">
-        <v>57348</v>
+        <v>78601</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3981,39 +3983,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>543122</v>
+        <v>543107</v>
       </c>
       <c r="R31" t="n">
-        <v>7208939</v>
+        <v>7209075</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4045,7 +4042,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4055,7 +4052,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4082,10 +4079,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120977996</v>
+        <v>120978036</v>
       </c>
       <c r="B32" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4127,10 +4124,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>543049</v>
+        <v>543123</v>
       </c>
       <c r="R32" t="n">
-        <v>7209349</v>
+        <v>7209054</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4162,7 +4159,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4172,7 +4169,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4199,10 +4196,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120977998</v>
+        <v>120978017</v>
       </c>
       <c r="B33" t="n">
-        <v>57348</v>
+        <v>79683</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4215,39 +4212,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>543044</v>
+        <v>543095</v>
       </c>
       <c r="R33" t="n">
-        <v>7209510</v>
+        <v>7209831</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4279,7 +4271,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4289,7 +4281,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4316,10 +4308,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120978002</v>
+        <v>120978004</v>
       </c>
       <c r="B34" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4356,10 +4348,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>543045</v>
+        <v>543044</v>
       </c>
       <c r="R34" t="n">
-        <v>7209613</v>
+        <v>7209633</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4391,7 +4383,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4401,7 +4393,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4428,10 +4420,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120978010</v>
+        <v>120978011</v>
       </c>
       <c r="B35" t="n">
-        <v>79708</v>
+        <v>79682</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4440,25 +4432,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4468,10 +4460,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>543067</v>
+        <v>543072</v>
       </c>
       <c r="R35" t="n">
-        <v>7209836</v>
+        <v>7209851</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4503,7 +4495,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4513,7 +4505,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4540,10 +4532,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120978031</v>
+        <v>120978035</v>
       </c>
       <c r="B36" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4580,10 +4572,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>543135</v>
+        <v>543116</v>
       </c>
       <c r="R36" t="n">
-        <v>7209283</v>
+        <v>7209226</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4615,7 +4607,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4625,7 +4617,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4652,10 +4644,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120978033</v>
+        <v>120978021</v>
       </c>
       <c r="B37" t="n">
-        <v>78598</v>
+        <v>91052</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4664,25 +4656,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1506</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4692,10 +4684,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>543133</v>
+        <v>543115</v>
       </c>
       <c r="R37" t="n">
-        <v>7209253</v>
+        <v>7209734</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4727,7 +4719,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4737,7 +4729,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4764,10 +4756,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120978054</v>
+        <v>120978044</v>
       </c>
       <c r="B38" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4804,10 +4796,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>543107</v>
+        <v>543123</v>
       </c>
       <c r="R38" t="n">
-        <v>7209075</v>
+        <v>7208937</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4839,7 +4831,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4849,7 +4841,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4876,10 +4868,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120978007</v>
+        <v>120978062</v>
       </c>
       <c r="B39" t="n">
-        <v>79680</v>
+        <v>78601</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4892,21 +4884,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4916,10 +4908,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>543068</v>
+        <v>543075</v>
       </c>
       <c r="R39" t="n">
-        <v>7209835</v>
+        <v>7209164</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4951,7 +4943,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4961,7 +4953,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4988,10 +4980,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120978015</v>
+        <v>120978002</v>
       </c>
       <c r="B40" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5028,10 +5020,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>543086</v>
+        <v>543045</v>
       </c>
       <c r="R40" t="n">
-        <v>7209826</v>
+        <v>7209613</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5063,7 +5055,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5073,7 +5065,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5100,10 +5092,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120978012</v>
+        <v>120978043</v>
       </c>
       <c r="B41" t="n">
-        <v>79715</v>
+        <v>57351</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5112,38 +5104,43 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>543072</v>
+        <v>543122</v>
       </c>
       <c r="R41" t="n">
-        <v>7209851</v>
+        <v>7208939</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5175,7 +5172,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5185,7 +5182,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5212,10 +5209,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120978009</v>
+        <v>120978020</v>
       </c>
       <c r="B42" t="n">
-        <v>79679</v>
+        <v>57462</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5224,38 +5221,42 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>103031</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>543069</v>
+        <v>543115</v>
       </c>
       <c r="R42" t="n">
-        <v>7209839</v>
+        <v>7209734</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5287,7 +5288,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5297,7 +5298,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5324,10 +5325,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120978011</v>
+        <v>120978027</v>
       </c>
       <c r="B43" t="n">
-        <v>79679</v>
+        <v>78601</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5340,21 +5341,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5364,10 +5365,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>543072</v>
+        <v>543112</v>
       </c>
       <c r="R43" t="n">
-        <v>7209851</v>
+        <v>7209467</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5399,7 +5400,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5409,7 +5410,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5436,10 +5437,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120978019</v>
+        <v>120978046</v>
       </c>
       <c r="B44" t="n">
-        <v>79708</v>
+        <v>78601</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5448,25 +5449,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5476,10 +5477,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>543161</v>
+        <v>543114</v>
       </c>
       <c r="R44" t="n">
-        <v>7209834</v>
+        <v>7208935</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5511,7 +5512,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5521,7 +5522,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5548,10 +5549,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120978022</v>
+        <v>120978052</v>
       </c>
       <c r="B45" t="n">
-        <v>90973</v>
+        <v>78601</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5564,21 +5565,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5588,10 +5589,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>543114</v>
+        <v>543096</v>
       </c>
       <c r="R45" t="n">
-        <v>7209734</v>
+        <v>7209059</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5623,7 +5624,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5633,7 +5634,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5660,10 +5661,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120978037</v>
+        <v>120978056</v>
       </c>
       <c r="B46" t="n">
-        <v>78598</v>
+        <v>90715</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5676,21 +5677,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5700,10 +5701,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>543124</v>
+        <v>543091</v>
       </c>
       <c r="R46" t="n">
-        <v>7209053</v>
+        <v>7209092</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5735,7 +5736,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5745,7 +5746,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5772,10 +5773,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120978000</v>
+        <v>120978015</v>
       </c>
       <c r="B47" t="n">
-        <v>57348</v>
+        <v>78601</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5788,39 +5789,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>543043</v>
+        <v>543086</v>
       </c>
       <c r="R47" t="n">
-        <v>7209590</v>
+        <v>7209826</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5852,7 +5848,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5862,7 +5858,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5889,10 +5885,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120978038</v>
+        <v>120978040</v>
       </c>
       <c r="B48" t="n">
-        <v>57348</v>
+        <v>78601</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5905,39 +5901,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>543133</v>
+        <v>543164</v>
       </c>
       <c r="R48" t="n">
-        <v>7209037</v>
+        <v>7208974</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5969,7 +5960,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5979,7 +5970,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6006,10 +5997,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120978046</v>
+        <v>120978006</v>
       </c>
       <c r="B49" t="n">
-        <v>78598</v>
+        <v>57351</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6022,34 +6013,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>543114</v>
+        <v>543075</v>
       </c>
       <c r="R49" t="n">
-        <v>7208935</v>
+        <v>7209798</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6081,7 +6077,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6091,7 +6087,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Påbörjat bohål</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6118,10 +6119,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120978026</v>
+        <v>120978055</v>
       </c>
       <c r="B50" t="n">
-        <v>57348</v>
+        <v>57351</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6154,7 +6155,7 @@
       <c r="I50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6163,10 +6164,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>543114</v>
+        <v>543091</v>
       </c>
       <c r="R50" t="n">
-        <v>7209471</v>
+        <v>7209093</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6198,7 +6199,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6208,7 +6209,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6235,10 +6236,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120978018</v>
+        <v>120978034</v>
       </c>
       <c r="B51" t="n">
-        <v>79708</v>
+        <v>57351</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6247,38 +6248,43 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>543095</v>
+        <v>543114</v>
       </c>
       <c r="R51" t="n">
-        <v>7209831</v>
+        <v>7209229</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6310,7 +6316,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6320,7 +6326,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6347,10 +6353,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120978005</v>
+        <v>120978012</v>
       </c>
       <c r="B52" t="n">
-        <v>57348</v>
+        <v>79718</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6359,43 +6365,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>543049</v>
+        <v>543072</v>
       </c>
       <c r="R52" t="n">
-        <v>7209680</v>
+        <v>7209851</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6427,7 +6428,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6437,7 +6438,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6464,10 +6465,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120978014</v>
+        <v>120978001</v>
       </c>
       <c r="B53" t="n">
-        <v>57348</v>
+        <v>79683</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6480,39 +6481,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>543091</v>
+        <v>543045</v>
       </c>
       <c r="R53" t="n">
-        <v>7209831</v>
+        <v>7209613</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6544,7 +6540,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6554,7 +6550,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6581,10 +6577,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120978028</v>
+        <v>120978060</v>
       </c>
       <c r="B54" t="n">
-        <v>57348</v>
+        <v>77548</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6597,39 +6593,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>543068</v>
+        <v>543079</v>
       </c>
       <c r="R54" t="n">
-        <v>7209436</v>
+        <v>7209176</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6661,7 +6652,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6671,7 +6662,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6698,10 +6689,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120978044</v>
+        <v>120978048</v>
       </c>
       <c r="B55" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6738,10 +6729,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>543123</v>
+        <v>543107</v>
       </c>
       <c r="R55" t="n">
-        <v>7208937</v>
+        <v>7209000</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6773,7 +6764,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6783,7 +6774,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6810,10 +6801,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120978039</v>
+        <v>120978061</v>
       </c>
       <c r="B56" t="n">
-        <v>78598</v>
+        <v>74708</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6826,21 +6817,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6850,10 +6841,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>543134</v>
+        <v>543075</v>
       </c>
       <c r="R56" t="n">
-        <v>7209039</v>
+        <v>7209164</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6885,7 +6876,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6895,7 +6886,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6922,10 +6913,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120978050</v>
+        <v>120978022</v>
       </c>
       <c r="B57" t="n">
-        <v>78598</v>
+        <v>90983</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6938,21 +6929,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6962,10 +6953,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>543101</v>
+        <v>543114</v>
       </c>
       <c r="R57" t="n">
-        <v>7209025</v>
+        <v>7209734</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6997,7 +6988,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7007,7 +6998,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7034,10 +7025,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120978049</v>
+        <v>120978000</v>
       </c>
       <c r="B58" t="n">
-        <v>90683</v>
+        <v>57351</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7050,34 +7041,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>543099</v>
+        <v>543043</v>
       </c>
       <c r="R58" t="n">
-        <v>7209028</v>
+        <v>7209590</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7109,7 +7105,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7119,7 +7115,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7146,10 +7142,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120978045</v>
+        <v>120977999</v>
       </c>
       <c r="B59" t="n">
-        <v>57348</v>
+        <v>78601</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7162,39 +7158,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>543114</v>
+        <v>543048</v>
       </c>
       <c r="R59" t="n">
-        <v>7208935</v>
+        <v>7209511</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7226,7 +7217,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7236,7 +7227,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7263,10 +7254,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120978051</v>
+        <v>120978013</v>
       </c>
       <c r="B60" t="n">
-        <v>57348</v>
+        <v>79717</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7275,43 +7266,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>543095</v>
+        <v>543076</v>
       </c>
       <c r="R60" t="n">
-        <v>7209049</v>
+        <v>7209851</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7343,7 +7329,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7353,7 +7339,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7380,10 +7366,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120977999</v>
+        <v>120978031</v>
       </c>
       <c r="B61" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7420,10 +7406,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>543048</v>
+        <v>543135</v>
       </c>
       <c r="R61" t="n">
-        <v>7209511</v>
+        <v>7209283</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7455,7 +7441,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7465,7 +7451,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7492,10 +7478,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120978003</v>
+        <v>120978030</v>
       </c>
       <c r="B62" t="n">
-        <v>82382</v>
+        <v>57504</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7508,34 +7494,38 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1312</v>
+        <v>103021</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>543045</v>
+        <v>543137</v>
       </c>
       <c r="R62" t="n">
-        <v>7209634</v>
+        <v>7209282</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7567,7 +7557,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7577,7 +7567,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7604,10 +7594,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120978008</v>
+        <v>120978018</v>
       </c>
       <c r="B63" t="n">
-        <v>78598</v>
+        <v>79711</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7616,25 +7606,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7644,10 +7634,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>543067</v>
+        <v>543095</v>
       </c>
       <c r="R63" t="n">
-        <v>7209836</v>
+        <v>7209831</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7679,7 +7669,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7689,7 +7679,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7716,10 +7706,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120978029</v>
+        <v>120978005</v>
       </c>
       <c r="B64" t="n">
-        <v>78598</v>
+        <v>57351</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7732,34 +7722,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>543068</v>
+        <v>543049</v>
       </c>
       <c r="R64" t="n">
-        <v>7209436</v>
+        <v>7209680</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7791,7 +7786,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7801,7 +7796,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7828,10 +7823,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120978047</v>
+        <v>120978053</v>
       </c>
       <c r="B65" t="n">
-        <v>90683</v>
+        <v>91090</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7844,21 +7839,16 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1108</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Harticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7871,7 +7861,7 @@
         <v>543105</v>
       </c>
       <c r="R65" t="n">
-        <v>7209001</v>
+        <v>7209074</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7903,7 +7893,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7913,7 +7903,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7940,10 +7930,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120978017</v>
+        <v>120977998</v>
       </c>
       <c r="B66" t="n">
-        <v>79680</v>
+        <v>57351</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7956,34 +7946,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>543095</v>
+        <v>543044</v>
       </c>
       <c r="R66" t="n">
-        <v>7209831</v>
+        <v>7209510</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -8015,7 +8010,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8025,7 +8020,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8052,10 +8047,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120978061</v>
+        <v>120978041</v>
       </c>
       <c r="B67" t="n">
-        <v>74705</v>
+        <v>57351</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8068,34 +8063,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>543075</v>
+        <v>543164</v>
       </c>
       <c r="R67" t="n">
-        <v>7209164</v>
+        <v>7208974</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8137,7 +8137,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD67" t="b">

--- a/artfynd/A 40936-2024 artfynd.xlsx
+++ b/artfynd/A 40936-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120978019</v>
+        <v>120978051</v>
       </c>
       <c r="B2" t="n">
-        <v>79711</v>
+        <v>57351</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543161</v>
+        <v>543095</v>
       </c>
       <c r="R2" t="n">
-        <v>7209834</v>
+        <v>7209049</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120978029</v>
+        <v>120978042</v>
       </c>
       <c r="B3" t="n">
-        <v>78601</v>
+        <v>57462</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,38 +804,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543068</v>
+        <v>543149</v>
       </c>
       <c r="R3" t="n">
-        <v>7209436</v>
+        <v>7208877</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120978051</v>
+        <v>120978019</v>
       </c>
       <c r="B4" t="n">
-        <v>57351</v>
+        <v>79711</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,43 +920,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543095</v>
+        <v>543161</v>
       </c>
       <c r="R4" t="n">
-        <v>7209049</v>
+        <v>7209834</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120978042</v>
+        <v>120978029</v>
       </c>
       <c r="B5" t="n">
-        <v>57462</v>
+        <v>78601</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,42 +1032,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543149</v>
+        <v>543068</v>
       </c>
       <c r="R5" t="n">
-        <v>7208877</v>
+        <v>7209436</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1244,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120978038</v>
+        <v>120978049</v>
       </c>
       <c r="B7" t="n">
-        <v>57351</v>
+        <v>90693</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,39 +1260,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543133</v>
+        <v>543099</v>
       </c>
       <c r="R7" t="n">
-        <v>7209037</v>
+        <v>7209028</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1324,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1334,7 +1329,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,7 +1356,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120977996</v>
+        <v>120978038</v>
       </c>
       <c r="B8" t="n">
         <v>57351</v>
@@ -1406,10 +1401,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543049</v>
+        <v>543133</v>
       </c>
       <c r="R8" t="n">
-        <v>7209349</v>
+        <v>7209037</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1441,7 +1436,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1451,7 +1446,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1478,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120978049</v>
+        <v>120977996</v>
       </c>
       <c r="B9" t="n">
-        <v>90693</v>
+        <v>57351</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,34 +1489,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>543099</v>
+        <v>543049</v>
       </c>
       <c r="R9" t="n">
-        <v>7209028</v>
+        <v>7209349</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -4644,10 +4644,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120978021</v>
+        <v>120978020</v>
       </c>
       <c r="B37" t="n">
-        <v>91052</v>
+        <v>57462</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4656,28 +4656,32 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1506</v>
+        <v>103031</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
@@ -4756,10 +4760,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120978044</v>
+        <v>120978021</v>
       </c>
       <c r="B38" t="n">
-        <v>78601</v>
+        <v>91052</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4768,25 +4772,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1506</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4796,10 +4800,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>543123</v>
+        <v>543115</v>
       </c>
       <c r="R38" t="n">
-        <v>7208937</v>
+        <v>7209734</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4831,7 +4835,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4841,7 +4845,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4868,7 +4872,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120978062</v>
+        <v>120978044</v>
       </c>
       <c r="B39" t="n">
         <v>78601</v>
@@ -4908,10 +4912,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>543075</v>
+        <v>543123</v>
       </c>
       <c r="R39" t="n">
-        <v>7209164</v>
+        <v>7208937</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4943,7 +4947,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4953,7 +4957,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4980,7 +4984,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120978002</v>
+        <v>120978062</v>
       </c>
       <c r="B40" t="n">
         <v>78601</v>
@@ -5020,10 +5024,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>543045</v>
+        <v>543075</v>
       </c>
       <c r="R40" t="n">
-        <v>7209613</v>
+        <v>7209164</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5055,7 +5059,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5065,7 +5069,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5092,10 +5096,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120978043</v>
+        <v>120978002</v>
       </c>
       <c r="B41" t="n">
-        <v>57351</v>
+        <v>78601</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5108,39 +5112,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>543122</v>
+        <v>543045</v>
       </c>
       <c r="R41" t="n">
-        <v>7208939</v>
+        <v>7209613</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5172,7 +5171,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5182,7 +5181,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5209,10 +5208,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120978020</v>
+        <v>120978043</v>
       </c>
       <c r="B42" t="n">
-        <v>57462</v>
+        <v>57351</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5221,20 +5220,20 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -5242,9 +5241,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5253,10 +5253,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>543115</v>
+        <v>543122</v>
       </c>
       <c r="R42" t="n">
-        <v>7209734</v>
+        <v>7208939</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5288,7 +5288,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -6913,10 +6913,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120978022</v>
+        <v>120978000</v>
       </c>
       <c r="B57" t="n">
-        <v>90983</v>
+        <v>57351</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6929,34 +6929,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>543114</v>
+        <v>543043</v>
       </c>
       <c r="R57" t="n">
-        <v>7209734</v>
+        <v>7209590</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6988,7 +6993,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6998,7 +7003,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7025,10 +7030,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120978000</v>
+        <v>120978022</v>
       </c>
       <c r="B58" t="n">
-        <v>57351</v>
+        <v>90983</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7041,39 +7046,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>543043</v>
+        <v>543114</v>
       </c>
       <c r="R58" t="n">
-        <v>7209590</v>
+        <v>7209734</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7105,7 +7105,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7115,7 +7115,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7142,10 +7142,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120977999</v>
+        <v>120978030</v>
       </c>
       <c r="B59" t="n">
-        <v>78601</v>
+        <v>57504</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7158,34 +7158,38 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>543048</v>
+        <v>543137</v>
       </c>
       <c r="R59" t="n">
-        <v>7209511</v>
+        <v>7209282</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7217,7 +7221,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7227,7 +7231,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7254,10 +7258,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120978013</v>
+        <v>120977999</v>
       </c>
       <c r="B60" t="n">
-        <v>79717</v>
+        <v>78601</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7266,20 +7270,20 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -7294,10 +7298,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>543076</v>
+        <v>543048</v>
       </c>
       <c r="R60" t="n">
-        <v>7209851</v>
+        <v>7209511</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7329,7 +7333,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7339,7 +7343,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7366,10 +7370,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120978031</v>
+        <v>120978013</v>
       </c>
       <c r="B61" t="n">
-        <v>78601</v>
+        <v>79717</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7378,20 +7382,20 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -7406,10 +7410,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>543135</v>
+        <v>543076</v>
       </c>
       <c r="R61" t="n">
-        <v>7209283</v>
+        <v>7209851</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7441,7 +7445,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7451,7 +7455,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7478,10 +7482,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120978030</v>
+        <v>120978031</v>
       </c>
       <c r="B62" t="n">
-        <v>57504</v>
+        <v>78601</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7494,38 +7498,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>543137</v>
+        <v>543135</v>
       </c>
       <c r="R62" t="n">
-        <v>7209282</v>
+        <v>7209283</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7557,7 +7557,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7567,7 +7567,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD62" t="b">

--- a/artfynd/A 40936-2024 artfynd.xlsx
+++ b/artfynd/A 40936-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120978051</v>
+        <v>120978019</v>
       </c>
       <c r="B2" t="n">
-        <v>57351</v>
+        <v>79711</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543095</v>
+        <v>543161</v>
       </c>
       <c r="R2" t="n">
-        <v>7209049</v>
+        <v>7209834</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120978042</v>
+        <v>120978029</v>
       </c>
       <c r="B3" t="n">
-        <v>57462</v>
+        <v>78601</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,42 +799,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543149</v>
+        <v>543068</v>
       </c>
       <c r="R3" t="n">
-        <v>7208877</v>
+        <v>7209436</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -871,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120978019</v>
+        <v>120978051</v>
       </c>
       <c r="B4" t="n">
-        <v>79711</v>
+        <v>57351</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,38 +911,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543161</v>
+        <v>543095</v>
       </c>
       <c r="R4" t="n">
-        <v>7209834</v>
+        <v>7209049</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -983,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120978029</v>
+        <v>120978042</v>
       </c>
       <c r="B5" t="n">
-        <v>78601</v>
+        <v>57462</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,38 +1028,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543068</v>
+        <v>543149</v>
       </c>
       <c r="R5" t="n">
-        <v>7209436</v>
+        <v>7208877</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -4196,10 +4196,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120978017</v>
+        <v>120978004</v>
       </c>
       <c r="B33" t="n">
-        <v>79683</v>
+        <v>78601</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4212,21 +4212,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>543095</v>
+        <v>543044</v>
       </c>
       <c r="R33" t="n">
-        <v>7209831</v>
+        <v>7209633</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4271,7 +4271,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4308,10 +4308,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120978004</v>
+        <v>120978011</v>
       </c>
       <c r="B34" t="n">
-        <v>78601</v>
+        <v>79682</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4324,21 +4324,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>543044</v>
+        <v>543072</v>
       </c>
       <c r="R34" t="n">
-        <v>7209633</v>
+        <v>7209851</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4393,7 +4393,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4420,10 +4420,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120978011</v>
+        <v>120978017</v>
       </c>
       <c r="B35" t="n">
-        <v>79682</v>
+        <v>79683</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4436,21 +4436,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4460,10 +4460,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>543072</v>
+        <v>543095</v>
       </c>
       <c r="R35" t="n">
-        <v>7209851</v>
+        <v>7209831</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4495,7 +4495,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4505,7 +4505,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -7706,7 +7706,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120978005</v>
+        <v>120977998</v>
       </c>
       <c r="B64" t="n">
         <v>57351</v>
@@ -7742,7 +7742,7 @@
       <c r="I64" t="inlineStr"/>
       <c r="M64" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7751,10 +7751,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>543049</v>
+        <v>543044</v>
       </c>
       <c r="R64" t="n">
-        <v>7209680</v>
+        <v>7209510</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7823,10 +7823,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120978053</v>
+        <v>120978005</v>
       </c>
       <c r="B65" t="n">
-        <v>91090</v>
+        <v>57351</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7839,29 +7839,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6040186</v>
+        <v>100109</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>543105</v>
+        <v>543049</v>
       </c>
       <c r="R65" t="n">
-        <v>7209074</v>
+        <v>7209680</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7893,7 +7903,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7903,7 +7913,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7930,10 +7940,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120977998</v>
+        <v>120978053</v>
       </c>
       <c r="B66" t="n">
-        <v>57351</v>
+        <v>91090</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7946,39 +7956,29 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>543044</v>
+        <v>543105</v>
       </c>
       <c r="R66" t="n">
-        <v>7209510</v>
+        <v>7209074</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -8010,7 +8010,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8020,7 +8020,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD66" t="b">

--- a/artfynd/A 40936-2024 artfynd.xlsx
+++ b/artfynd/A 40936-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120978019</v>
+        <v>120978015</v>
       </c>
       <c r="B2" t="n">
-        <v>79711</v>
+        <v>78601</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543161</v>
+        <v>543086</v>
       </c>
       <c r="R2" t="n">
-        <v>7209834</v>
+        <v>7209826</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120978029</v>
+        <v>120978035</v>
       </c>
       <c r="B3" t="n">
         <v>78601</v>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543068</v>
+        <v>543116</v>
       </c>
       <c r="R3" t="n">
-        <v>7209436</v>
+        <v>7209226</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120978051</v>
+        <v>120978039</v>
       </c>
       <c r="B4" t="n">
-        <v>57351</v>
+        <v>78601</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,39 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543095</v>
+        <v>543134</v>
       </c>
       <c r="R4" t="n">
-        <v>7209049</v>
+        <v>7209039</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120978042</v>
+        <v>120978032</v>
       </c>
       <c r="B5" t="n">
-        <v>57462</v>
+        <v>57351</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,20 +1023,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1049,9 +1044,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1060,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543149</v>
+        <v>543135</v>
       </c>
       <c r="R5" t="n">
-        <v>7208877</v>
+        <v>7209257</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1095,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120978009</v>
+        <v>120978013</v>
       </c>
       <c r="B6" t="n">
-        <v>79682</v>
+        <v>79717</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,25 +1140,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1172,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543069</v>
+        <v>543076</v>
       </c>
       <c r="R6" t="n">
-        <v>7209839</v>
+        <v>7209851</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1207,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120978049</v>
+        <v>120978051</v>
       </c>
       <c r="B7" t="n">
-        <v>90693</v>
+        <v>57351</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,34 +1256,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543099</v>
+        <v>543095</v>
       </c>
       <c r="R7" t="n">
-        <v>7209028</v>
+        <v>7209049</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1319,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120978038</v>
+        <v>120978001</v>
       </c>
       <c r="B8" t="n">
-        <v>57351</v>
+        <v>79683</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1372,39 +1373,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543133</v>
+        <v>543045</v>
       </c>
       <c r="R8" t="n">
-        <v>7209037</v>
+        <v>7209613</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1436,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1446,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120977996</v>
+        <v>120978030</v>
       </c>
       <c r="B9" t="n">
-        <v>57351</v>
+        <v>57504</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,27 +1485,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1518,10 +1513,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>543049</v>
+        <v>543137</v>
       </c>
       <c r="R9" t="n">
-        <v>7209349</v>
+        <v>7209282</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1553,7 +1548,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1563,7 +1558,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1590,10 +1585,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120978063</v>
+        <v>120978022</v>
       </c>
       <c r="B10" t="n">
-        <v>78601</v>
+        <v>90983</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1606,21 +1601,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1630,10 +1625,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>543074</v>
+        <v>543114</v>
       </c>
       <c r="R10" t="n">
-        <v>7209182</v>
+        <v>7209734</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1665,7 +1660,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1675,7 +1670,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,10 +1697,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120978008</v>
+        <v>120978041</v>
       </c>
       <c r="B11" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1718,34 +1713,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>543067</v>
+        <v>543164</v>
       </c>
       <c r="R11" t="n">
-        <v>7209836</v>
+        <v>7208974</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1814,10 +1814,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120978037</v>
+        <v>120977997</v>
       </c>
       <c r="B12" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1830,34 +1830,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>543124</v>
+        <v>543057</v>
       </c>
       <c r="R12" t="n">
-        <v>7209053</v>
+        <v>7209403</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1889,7 +1894,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1899,7 +1904,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1926,10 +1931,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120978039</v>
+        <v>120978042</v>
       </c>
       <c r="B13" t="n">
-        <v>78601</v>
+        <v>57462</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1938,38 +1943,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>543134</v>
+        <v>543149</v>
       </c>
       <c r="R13" t="n">
-        <v>7209039</v>
+        <v>7208877</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2001,7 +2010,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2011,7 +2020,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2038,10 +2047,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120978014</v>
+        <v>120978046</v>
       </c>
       <c r="B14" t="n">
-        <v>57351</v>
+        <v>78601</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2054,39 +2063,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>543091</v>
+        <v>543114</v>
       </c>
       <c r="R14" t="n">
-        <v>7209831</v>
+        <v>7208935</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2118,7 +2122,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2128,7 +2132,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2155,10 +2159,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120978026</v>
+        <v>120978025</v>
       </c>
       <c r="B15" t="n">
-        <v>57351</v>
+        <v>78601</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2171,39 +2175,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>543114</v>
+        <v>543116</v>
       </c>
       <c r="R15" t="n">
-        <v>7209471</v>
+        <v>7209729</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2235,7 +2234,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2245,7 +2244,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2272,10 +2271,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120978025</v>
+        <v>120978000</v>
       </c>
       <c r="B16" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2288,34 +2287,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>543116</v>
+        <v>543043</v>
       </c>
       <c r="R16" t="n">
-        <v>7209729</v>
+        <v>7209590</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2347,7 +2351,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2357,7 +2361,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2384,10 +2388,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120978010</v>
+        <v>120978043</v>
       </c>
       <c r="B17" t="n">
-        <v>79711</v>
+        <v>57351</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2396,38 +2400,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>543067</v>
+        <v>543122</v>
       </c>
       <c r="R17" t="n">
-        <v>7209836</v>
+        <v>7208939</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2459,7 +2468,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2469,7 +2478,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2496,10 +2505,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120978023</v>
+        <v>120978040</v>
       </c>
       <c r="B18" t="n">
-        <v>90693</v>
+        <v>78601</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2512,21 +2521,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2536,10 +2545,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>543114</v>
+        <v>543164</v>
       </c>
       <c r="R18" t="n">
-        <v>7209734</v>
+        <v>7208974</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2571,7 +2580,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2581,7 +2590,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2608,10 +2617,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120978003</v>
+        <v>120978012</v>
       </c>
       <c r="B19" t="n">
-        <v>82385</v>
+        <v>79718</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2620,25 +2629,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2648,10 +2657,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>543045</v>
+        <v>543072</v>
       </c>
       <c r="R19" t="n">
-        <v>7209634</v>
+        <v>7209851</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2683,7 +2692,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2693,7 +2702,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2720,10 +2729,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120978047</v>
+        <v>120978020</v>
       </c>
       <c r="B20" t="n">
-        <v>90693</v>
+        <v>57462</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2732,38 +2741,42 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1108</v>
+        <v>103031</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>543105</v>
+        <v>543115</v>
       </c>
       <c r="R20" t="n">
-        <v>7209001</v>
+        <v>7209734</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2795,7 +2808,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2805,7 +2818,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2832,10 +2845,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120978024</v>
+        <v>120978007</v>
       </c>
       <c r="B21" t="n">
-        <v>91090</v>
+        <v>79683</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2848,16 +2861,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6040186</v>
+        <v>2081</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2867,10 +2885,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>543114</v>
+        <v>543068</v>
       </c>
       <c r="R21" t="n">
-        <v>7209731</v>
+        <v>7209835</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2902,7 +2920,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2912,7 +2930,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2939,7 +2957,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120978028</v>
+        <v>120978055</v>
       </c>
       <c r="B22" t="n">
         <v>57351</v>
@@ -2984,10 +3002,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>543068</v>
+        <v>543091</v>
       </c>
       <c r="R22" t="n">
-        <v>7209436</v>
+        <v>7209093</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3019,7 +3037,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3029,7 +3047,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3056,10 +3074,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120978016</v>
+        <v>120978014</v>
       </c>
       <c r="B23" t="n">
-        <v>79682</v>
+        <v>57351</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3072,31 +3090,36 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>543095</v>
+        <v>543091</v>
       </c>
       <c r="R23" t="n">
         <v>7209831</v>
@@ -3131,7 +3154,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3141,7 +3164,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3168,10 +3191,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120978059</v>
+        <v>120978009</v>
       </c>
       <c r="B24" t="n">
-        <v>78601</v>
+        <v>79682</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3184,21 +3207,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3208,10 +3231,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>543087</v>
+        <v>543069</v>
       </c>
       <c r="R24" t="n">
-        <v>7209098</v>
+        <v>7209839</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3243,7 +3266,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3253,7 +3276,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3280,10 +3303,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120978032</v>
+        <v>120978021</v>
       </c>
       <c r="B25" t="n">
-        <v>57351</v>
+        <v>91052</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3292,43 +3315,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>1506</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>543135</v>
+        <v>543115</v>
       </c>
       <c r="R25" t="n">
-        <v>7209257</v>
+        <v>7209734</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3360,7 +3378,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3370,7 +3388,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3397,10 +3415,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120978045</v>
+        <v>120978044</v>
       </c>
       <c r="B26" t="n">
-        <v>57351</v>
+        <v>78601</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3413,39 +3431,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>543114</v>
+        <v>543123</v>
       </c>
       <c r="R26" t="n">
-        <v>7208935</v>
+        <v>7208937</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3477,7 +3490,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3487,7 +3500,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3514,10 +3527,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120978007</v>
+        <v>120978027</v>
       </c>
       <c r="B27" t="n">
-        <v>79683</v>
+        <v>78601</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3530,21 +3543,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3554,10 +3567,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>543068</v>
+        <v>543112</v>
       </c>
       <c r="R27" t="n">
-        <v>7209835</v>
+        <v>7209467</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3589,7 +3602,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3599,7 +3612,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3626,7 +3639,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120978033</v>
+        <v>120978062</v>
       </c>
       <c r="B28" t="n">
         <v>78601</v>
@@ -3666,10 +3679,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>543133</v>
+        <v>543075</v>
       </c>
       <c r="R28" t="n">
-        <v>7209253</v>
+        <v>7209164</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3701,7 +3714,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3711,7 +3724,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3850,7 +3863,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120977997</v>
+        <v>120978028</v>
       </c>
       <c r="B30" t="n">
         <v>57351</v>
@@ -3886,7 +3899,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3895,10 +3908,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>543057</v>
+        <v>543068</v>
       </c>
       <c r="R30" t="n">
-        <v>7209403</v>
+        <v>7209436</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3930,7 +3943,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3940,7 +3953,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3967,10 +3980,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120978054</v>
+        <v>120978056</v>
       </c>
       <c r="B31" t="n">
-        <v>78601</v>
+        <v>90715</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3983,21 +3996,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4007,10 +4020,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>543107</v>
+        <v>543091</v>
       </c>
       <c r="R31" t="n">
-        <v>7209075</v>
+        <v>7209092</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4042,7 +4055,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4052,7 +4065,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4079,10 +4092,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120978036</v>
+        <v>120978063</v>
       </c>
       <c r="B32" t="n">
-        <v>57351</v>
+        <v>78601</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4095,39 +4108,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>543123</v>
+        <v>543074</v>
       </c>
       <c r="R32" t="n">
-        <v>7209054</v>
+        <v>7209182</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4159,7 +4167,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4169,7 +4177,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4196,10 +4204,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120978004</v>
+        <v>120978061</v>
       </c>
       <c r="B33" t="n">
-        <v>78601</v>
+        <v>74708</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4212,21 +4220,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4236,10 +4244,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>543044</v>
+        <v>543075</v>
       </c>
       <c r="R33" t="n">
-        <v>7209633</v>
+        <v>7209164</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4271,7 +4279,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4281,7 +4289,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4308,10 +4316,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120978011</v>
+        <v>120978006</v>
       </c>
       <c r="B34" t="n">
-        <v>79682</v>
+        <v>57351</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4324,34 +4332,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>543072</v>
+        <v>543075</v>
       </c>
       <c r="R34" t="n">
-        <v>7209851</v>
+        <v>7209798</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4383,7 +4396,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4393,7 +4406,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Påbörjat bohål</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4420,10 +4438,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120978017</v>
+        <v>120977996</v>
       </c>
       <c r="B35" t="n">
-        <v>79683</v>
+        <v>57351</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4436,34 +4454,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>543095</v>
+        <v>543049</v>
       </c>
       <c r="R35" t="n">
-        <v>7209831</v>
+        <v>7209349</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4495,7 +4518,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4505,7 +4528,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4532,7 +4555,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120978035</v>
+        <v>120978052</v>
       </c>
       <c r="B36" t="n">
         <v>78601</v>
@@ -4572,10 +4595,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>543116</v>
+        <v>543096</v>
       </c>
       <c r="R36" t="n">
-        <v>7209226</v>
+        <v>7209059</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4607,7 +4630,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4617,7 +4640,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4644,10 +4667,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120978020</v>
+        <v>120978037</v>
       </c>
       <c r="B37" t="n">
-        <v>57462</v>
+        <v>78601</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4656,42 +4679,38 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>543115</v>
+        <v>543124</v>
       </c>
       <c r="R37" t="n">
-        <v>7209734</v>
+        <v>7209053</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4723,7 +4742,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4733,7 +4752,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4760,10 +4779,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120978021</v>
+        <v>120978060</v>
       </c>
       <c r="B38" t="n">
-        <v>91052</v>
+        <v>77548</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4772,25 +4791,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1506</v>
+        <v>314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4800,10 +4819,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>543115</v>
+        <v>543079</v>
       </c>
       <c r="R38" t="n">
-        <v>7209734</v>
+        <v>7209176</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4835,7 +4854,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4845,7 +4864,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4872,10 +4891,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120978044</v>
+        <v>120978053</v>
       </c>
       <c r="B39" t="n">
-        <v>78601</v>
+        <v>91090</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4888,21 +4907,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4912,10 +4926,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>543123</v>
+        <v>543105</v>
       </c>
       <c r="R39" t="n">
-        <v>7208937</v>
+        <v>7209074</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4947,7 +4961,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4957,7 +4971,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4984,7 +4998,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120978062</v>
+        <v>120978008</v>
       </c>
       <c r="B40" t="n">
         <v>78601</v>
@@ -5024,10 +5038,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>543075</v>
+        <v>543067</v>
       </c>
       <c r="R40" t="n">
-        <v>7209164</v>
+        <v>7209836</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5059,7 +5073,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5069,7 +5083,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5096,10 +5110,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120978002</v>
+        <v>120978016</v>
       </c>
       <c r="B41" t="n">
-        <v>78601</v>
+        <v>79682</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5112,21 +5126,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5136,10 +5150,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>543045</v>
+        <v>543095</v>
       </c>
       <c r="R41" t="n">
-        <v>7209613</v>
+        <v>7209831</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5171,7 +5185,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5181,7 +5195,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5208,10 +5222,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120978043</v>
+        <v>120978059</v>
       </c>
       <c r="B42" t="n">
-        <v>57351</v>
+        <v>78601</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5224,39 +5238,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>543122</v>
+        <v>543087</v>
       </c>
       <c r="R42" t="n">
-        <v>7208939</v>
+        <v>7209098</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5288,7 +5297,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5298,7 +5307,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5325,10 +5334,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120978027</v>
+        <v>120978003</v>
       </c>
       <c r="B43" t="n">
-        <v>78601</v>
+        <v>82385</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5341,21 +5350,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5365,10 +5374,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>543112</v>
+        <v>543045</v>
       </c>
       <c r="R43" t="n">
-        <v>7209467</v>
+        <v>7209634</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5400,7 +5409,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5410,7 +5419,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5437,7 +5446,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120978046</v>
+        <v>120978048</v>
       </c>
       <c r="B44" t="n">
         <v>78601</v>
@@ -5477,10 +5486,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>543114</v>
+        <v>543107</v>
       </c>
       <c r="R44" t="n">
-        <v>7208935</v>
+        <v>7209000</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5512,7 +5521,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5522,7 +5531,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5549,7 +5558,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120978052</v>
+        <v>120978002</v>
       </c>
       <c r="B45" t="n">
         <v>78601</v>
@@ -5589,10 +5598,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>543096</v>
+        <v>543045</v>
       </c>
       <c r="R45" t="n">
-        <v>7209059</v>
+        <v>7209613</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5624,7 +5633,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5634,7 +5643,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5661,10 +5670,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120978056</v>
+        <v>120978019</v>
       </c>
       <c r="B46" t="n">
-        <v>90715</v>
+        <v>79711</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5673,25 +5682,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5701,10 +5710,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>543091</v>
+        <v>543161</v>
       </c>
       <c r="R46" t="n">
-        <v>7209092</v>
+        <v>7209834</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5736,7 +5745,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5746,7 +5755,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5773,7 +5782,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120978015</v>
+        <v>120978054</v>
       </c>
       <c r="B47" t="n">
         <v>78601</v>
@@ -5813,10 +5822,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>543086</v>
+        <v>543107</v>
       </c>
       <c r="R47" t="n">
-        <v>7209826</v>
+        <v>7209075</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5848,7 +5857,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5858,7 +5867,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5885,10 +5894,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120978040</v>
+        <v>120978036</v>
       </c>
       <c r="B48" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5901,34 +5910,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>543164</v>
+        <v>543123</v>
       </c>
       <c r="R48" t="n">
-        <v>7208974</v>
+        <v>7209054</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5960,7 +5974,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5970,7 +5984,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5997,7 +6011,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120978006</v>
+        <v>120978034</v>
       </c>
       <c r="B49" t="n">
         <v>57351</v>
@@ -6033,7 +6047,7 @@
       <c r="I49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6042,10 +6056,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>543075</v>
+        <v>543114</v>
       </c>
       <c r="R49" t="n">
-        <v>7209798</v>
+        <v>7209229</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6077,7 +6091,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6087,12 +6101,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:37</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Påbörjat bohål</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6119,10 +6128,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120978055</v>
+        <v>120977999</v>
       </c>
       <c r="B50" t="n">
-        <v>57351</v>
+        <v>78601</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6135,39 +6144,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>543091</v>
+        <v>543048</v>
       </c>
       <c r="R50" t="n">
-        <v>7209093</v>
+        <v>7209511</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6199,7 +6203,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6209,7 +6213,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6236,10 +6240,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120978034</v>
+        <v>120978018</v>
       </c>
       <c r="B51" t="n">
-        <v>57351</v>
+        <v>79711</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6248,43 +6252,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>543114</v>
+        <v>543095</v>
       </c>
       <c r="R51" t="n">
-        <v>7209229</v>
+        <v>7209831</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6316,7 +6315,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6326,7 +6325,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6353,10 +6352,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120978012</v>
+        <v>120978010</v>
       </c>
       <c r="B52" t="n">
-        <v>79718</v>
+        <v>79711</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6369,21 +6368,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6393,10 +6392,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>543072</v>
+        <v>543067</v>
       </c>
       <c r="R52" t="n">
-        <v>7209851</v>
+        <v>7209836</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6428,7 +6427,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6438,7 +6437,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6465,10 +6464,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120978001</v>
+        <v>120978047</v>
       </c>
       <c r="B53" t="n">
-        <v>79683</v>
+        <v>90693</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6481,21 +6480,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6505,10 +6504,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>543045</v>
+        <v>543105</v>
       </c>
       <c r="R53" t="n">
-        <v>7209613</v>
+        <v>7209001</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6540,7 +6539,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6550,7 +6549,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6577,10 +6576,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120978060</v>
+        <v>120978033</v>
       </c>
       <c r="B54" t="n">
-        <v>77548</v>
+        <v>78601</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6593,21 +6592,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6617,10 +6616,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>543079</v>
+        <v>543133</v>
       </c>
       <c r="R54" t="n">
-        <v>7209176</v>
+        <v>7209253</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6652,7 +6651,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6662,7 +6661,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6689,10 +6688,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120978048</v>
+        <v>120978038</v>
       </c>
       <c r="B55" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6705,34 +6704,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>543107</v>
+        <v>543133</v>
       </c>
       <c r="R55" t="n">
-        <v>7209000</v>
+        <v>7209037</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6764,7 +6768,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6774,7 +6778,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6801,10 +6805,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120978061</v>
+        <v>120977998</v>
       </c>
       <c r="B56" t="n">
-        <v>74708</v>
+        <v>57351</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6817,34 +6821,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>543075</v>
+        <v>543044</v>
       </c>
       <c r="R56" t="n">
-        <v>7209164</v>
+        <v>7209510</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6876,7 +6885,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6886,7 +6895,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6913,7 +6922,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120978000</v>
+        <v>120978045</v>
       </c>
       <c r="B57" t="n">
         <v>57351</v>
@@ -6949,7 +6958,7 @@
       <c r="I57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6958,10 +6967,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>543043</v>
+        <v>543114</v>
       </c>
       <c r="R57" t="n">
-        <v>7209590</v>
+        <v>7208935</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6993,7 +7002,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7003,7 +7012,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7030,10 +7039,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120978022</v>
+        <v>120978011</v>
       </c>
       <c r="B58" t="n">
-        <v>90983</v>
+        <v>79682</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7046,21 +7055,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7070,10 +7079,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>543114</v>
+        <v>543072</v>
       </c>
       <c r="R58" t="n">
-        <v>7209734</v>
+        <v>7209851</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7105,7 +7114,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7115,7 +7124,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7142,10 +7151,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120978030</v>
+        <v>120978026</v>
       </c>
       <c r="B59" t="n">
-        <v>57504</v>
+        <v>57351</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7158,26 +7167,27 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7186,10 +7196,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>543137</v>
+        <v>543114</v>
       </c>
       <c r="R59" t="n">
-        <v>7209282</v>
+        <v>7209471</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7221,7 +7231,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7231,7 +7241,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7258,10 +7268,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120977999</v>
+        <v>120978005</v>
       </c>
       <c r="B60" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7274,34 +7284,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>543048</v>
+        <v>543049</v>
       </c>
       <c r="R60" t="n">
-        <v>7209511</v>
+        <v>7209680</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7333,7 +7348,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7343,7 +7358,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7370,10 +7385,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120978013</v>
+        <v>120978049</v>
       </c>
       <c r="B61" t="n">
-        <v>79717</v>
+        <v>90693</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7382,25 +7397,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6463</v>
+        <v>1108</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7410,10 +7425,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>543076</v>
+        <v>543099</v>
       </c>
       <c r="R61" t="n">
-        <v>7209851</v>
+        <v>7209028</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7445,7 +7460,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7455,7 +7470,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7482,10 +7497,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120978031</v>
+        <v>120978017</v>
       </c>
       <c r="B62" t="n">
-        <v>78601</v>
+        <v>79683</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7498,21 +7513,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7522,10 +7537,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>543135</v>
+        <v>543095</v>
       </c>
       <c r="R62" t="n">
-        <v>7209283</v>
+        <v>7209831</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7557,7 +7572,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7567,7 +7582,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7594,10 +7609,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120978018</v>
+        <v>120978029</v>
       </c>
       <c r="B63" t="n">
-        <v>79711</v>
+        <v>78601</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7606,25 +7621,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7634,10 +7649,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>543095</v>
+        <v>543068</v>
       </c>
       <c r="R63" t="n">
-        <v>7209831</v>
+        <v>7209436</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7669,7 +7684,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7679,7 +7694,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7706,10 +7721,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120977998</v>
+        <v>120978031</v>
       </c>
       <c r="B64" t="n">
-        <v>57351</v>
+        <v>78601</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7722,39 +7737,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>543044</v>
+        <v>543135</v>
       </c>
       <c r="R64" t="n">
-        <v>7209510</v>
+        <v>7209283</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7786,7 +7796,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7796,7 +7806,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7823,10 +7833,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120978005</v>
+        <v>120978024</v>
       </c>
       <c r="B65" t="n">
-        <v>57351</v>
+        <v>91090</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7839,39 +7849,29 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>543049</v>
+        <v>543114</v>
       </c>
       <c r="R65" t="n">
-        <v>7209680</v>
+        <v>7209731</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7903,7 +7903,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7913,7 +7913,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7940,10 +7940,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120978053</v>
+        <v>120978023</v>
       </c>
       <c r="B66" t="n">
-        <v>91090</v>
+        <v>90693</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7956,16 +7956,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6040186</v>
+        <v>1108</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7975,10 +7980,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>543105</v>
+        <v>543114</v>
       </c>
       <c r="R66" t="n">
-        <v>7209074</v>
+        <v>7209734</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -8010,7 +8015,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8020,7 +8025,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8047,10 +8052,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120978041</v>
+        <v>120978004</v>
       </c>
       <c r="B67" t="n">
-        <v>57351</v>
+        <v>78601</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8063,39 +8068,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>543164</v>
+        <v>543044</v>
       </c>
       <c r="R67" t="n">
-        <v>7208974</v>
+        <v>7209633</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8137,7 +8137,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD67" t="b">

--- a/artfynd/A 40936-2024 artfynd.xlsx
+++ b/artfynd/A 40936-2024 artfynd.xlsx
@@ -1931,10 +1931,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120978042</v>
+        <v>120978046</v>
       </c>
       <c r="B13" t="n">
-        <v>57462</v>
+        <v>78601</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1943,42 +1943,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>543149</v>
+        <v>543114</v>
       </c>
       <c r="R13" t="n">
-        <v>7208877</v>
+        <v>7208935</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2010,7 +2006,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2020,7 +2016,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2047,7 +2043,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120978046</v>
+        <v>120978025</v>
       </c>
       <c r="B14" t="n">
         <v>78601</v>
@@ -2087,10 +2083,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>543114</v>
+        <v>543116</v>
       </c>
       <c r="R14" t="n">
-        <v>7208935</v>
+        <v>7209729</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2122,7 +2118,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2132,7 +2128,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2159,10 +2155,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120978025</v>
+        <v>120978000</v>
       </c>
       <c r="B15" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2175,34 +2171,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>543116</v>
+        <v>543043</v>
       </c>
       <c r="R15" t="n">
-        <v>7209729</v>
+        <v>7209590</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2234,7 +2235,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2244,7 +2245,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2271,10 +2272,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120978000</v>
+        <v>120978042</v>
       </c>
       <c r="B16" t="n">
-        <v>57351</v>
+        <v>57462</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2283,20 +2284,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2304,10 +2305,9 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2316,10 +2316,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>543043</v>
+        <v>543149</v>
       </c>
       <c r="R16" t="n">
-        <v>7209590</v>
+        <v>7208877</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2388,10 +2388,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120978043</v>
+        <v>120978040</v>
       </c>
       <c r="B17" t="n">
-        <v>57351</v>
+        <v>78601</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2404,39 +2404,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>543122</v>
+        <v>543164</v>
       </c>
       <c r="R17" t="n">
-        <v>7208939</v>
+        <v>7208974</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2468,7 +2463,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2478,7 +2473,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2505,10 +2500,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120978040</v>
+        <v>120978043</v>
       </c>
       <c r="B18" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2521,34 +2516,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>543164</v>
+        <v>543122</v>
       </c>
       <c r="R18" t="n">
-        <v>7208974</v>
+        <v>7208939</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2729,10 +2729,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120978020</v>
+        <v>120978007</v>
       </c>
       <c r="B20" t="n">
-        <v>57462</v>
+        <v>79683</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2741,42 +2741,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103031</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>543115</v>
+        <v>543068</v>
       </c>
       <c r="R20" t="n">
-        <v>7209734</v>
+        <v>7209835</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2808,7 +2804,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2818,7 +2814,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2845,10 +2841,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120978007</v>
+        <v>120978020</v>
       </c>
       <c r="B21" t="n">
-        <v>79683</v>
+        <v>57462</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2857,38 +2853,42 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>103031</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>543068</v>
+        <v>543115</v>
       </c>
       <c r="R21" t="n">
-        <v>7209835</v>
+        <v>7209734</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3303,10 +3303,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120978021</v>
+        <v>120978044</v>
       </c>
       <c r="B25" t="n">
-        <v>91052</v>
+        <v>78601</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3315,25 +3315,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1506</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>543115</v>
+        <v>543123</v>
       </c>
       <c r="R25" t="n">
-        <v>7209734</v>
+        <v>7208937</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3415,7 +3415,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120978044</v>
+        <v>120978027</v>
       </c>
       <c r="B26" t="n">
         <v>78601</v>
@@ -3455,10 +3455,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>543123</v>
+        <v>543112</v>
       </c>
       <c r="R26" t="n">
-        <v>7208937</v>
+        <v>7209467</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3490,7 +3490,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3527,7 +3527,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120978027</v>
+        <v>120978062</v>
       </c>
       <c r="B27" t="n">
         <v>78601</v>
@@ -3567,10 +3567,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>543112</v>
+        <v>543075</v>
       </c>
       <c r="R27" t="n">
-        <v>7209467</v>
+        <v>7209164</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3639,7 +3639,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120978062</v>
+        <v>120978050</v>
       </c>
       <c r="B28" t="n">
         <v>78601</v>
@@ -3679,10 +3679,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>543075</v>
+        <v>543101</v>
       </c>
       <c r="R28" t="n">
-        <v>7209164</v>
+        <v>7209025</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3751,10 +3751,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120978050</v>
+        <v>120978021</v>
       </c>
       <c r="B29" t="n">
-        <v>78601</v>
+        <v>91052</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3763,25 +3763,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1506</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3791,10 +3791,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>543101</v>
+        <v>543115</v>
       </c>
       <c r="R29" t="n">
-        <v>7209025</v>
+        <v>7209734</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3826,7 +3826,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -5334,10 +5334,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120978003</v>
+        <v>120978048</v>
       </c>
       <c r="B43" t="n">
-        <v>82385</v>
+        <v>78601</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5350,21 +5350,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5374,10 +5374,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>543045</v>
+        <v>543107</v>
       </c>
       <c r="R43" t="n">
-        <v>7209634</v>
+        <v>7209000</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5409,7 +5409,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5419,7 +5419,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5446,7 +5446,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120978048</v>
+        <v>120978002</v>
       </c>
       <c r="B44" t="n">
         <v>78601</v>
@@ -5486,10 +5486,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>543107</v>
+        <v>543045</v>
       </c>
       <c r="R44" t="n">
-        <v>7209000</v>
+        <v>7209613</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5521,7 +5521,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5558,10 +5558,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120978002</v>
+        <v>120978019</v>
       </c>
       <c r="B45" t="n">
-        <v>78601</v>
+        <v>79711</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5570,25 +5570,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5598,10 +5598,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>543045</v>
+        <v>543161</v>
       </c>
       <c r="R45" t="n">
-        <v>7209613</v>
+        <v>7209834</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5633,7 +5633,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5670,10 +5670,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120978019</v>
+        <v>120978054</v>
       </c>
       <c r="B46" t="n">
-        <v>79711</v>
+        <v>78601</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5682,25 +5682,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5710,10 +5710,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>543161</v>
+        <v>543107</v>
       </c>
       <c r="R46" t="n">
-        <v>7209834</v>
+        <v>7209075</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5745,7 +5745,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5755,7 +5755,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5782,10 +5782,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120978054</v>
+        <v>120978036</v>
       </c>
       <c r="B47" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5798,34 +5798,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>543107</v>
+        <v>543123</v>
       </c>
       <c r="R47" t="n">
-        <v>7209075</v>
+        <v>7209054</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5857,7 +5862,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5867,7 +5872,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5894,7 +5899,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120978036</v>
+        <v>120978034</v>
       </c>
       <c r="B48" t="n">
         <v>57351</v>
@@ -5930,7 +5935,7 @@
       <c r="I48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5939,10 +5944,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>543123</v>
+        <v>543114</v>
       </c>
       <c r="R48" t="n">
-        <v>7209054</v>
+        <v>7209229</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5974,7 +5979,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5984,7 +5989,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6011,10 +6016,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120978034</v>
+        <v>120978003</v>
       </c>
       <c r="B49" t="n">
-        <v>57351</v>
+        <v>82385</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6027,39 +6032,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>543114</v>
+        <v>543045</v>
       </c>
       <c r="R49" t="n">
-        <v>7209229</v>
+        <v>7209634</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6101,7 +6101,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6464,10 +6464,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120978047</v>
+        <v>120978038</v>
       </c>
       <c r="B53" t="n">
-        <v>90693</v>
+        <v>57351</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6480,34 +6480,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>543105</v>
+        <v>543133</v>
       </c>
       <c r="R53" t="n">
-        <v>7209001</v>
+        <v>7209037</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6539,7 +6544,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6549,7 +6554,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6576,10 +6581,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120978033</v>
+        <v>120977998</v>
       </c>
       <c r="B54" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6592,34 +6597,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>543133</v>
+        <v>543044</v>
       </c>
       <c r="R54" t="n">
-        <v>7209253</v>
+        <v>7209510</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6651,7 +6661,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6661,7 +6671,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6688,7 +6698,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120978038</v>
+        <v>120978045</v>
       </c>
       <c r="B55" t="n">
         <v>57351</v>
@@ -6733,10 +6743,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>543133</v>
+        <v>543114</v>
       </c>
       <c r="R55" t="n">
-        <v>7209037</v>
+        <v>7208935</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6768,7 +6778,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6778,7 +6788,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6805,10 +6815,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120977998</v>
+        <v>120978047</v>
       </c>
       <c r="B56" t="n">
-        <v>57351</v>
+        <v>90693</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6821,39 +6831,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>543044</v>
+        <v>543105</v>
       </c>
       <c r="R56" t="n">
-        <v>7209510</v>
+        <v>7209001</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6885,7 +6890,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6895,7 +6900,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6922,10 +6927,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120978045</v>
+        <v>120978033</v>
       </c>
       <c r="B57" t="n">
-        <v>57351</v>
+        <v>78601</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6938,39 +6943,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>543114</v>
+        <v>543133</v>
       </c>
       <c r="R57" t="n">
-        <v>7208935</v>
+        <v>7209253</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -7002,7 +7002,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 40936-2024 artfynd.xlsx
+++ b/artfynd/A 40936-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120978015</v>
+        <v>120978031</v>
       </c>
       <c r="B2" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543086</v>
+        <v>543135</v>
       </c>
       <c r="R2" t="n">
-        <v>7209826</v>
+        <v>7209283</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120978035</v>
+        <v>120978054</v>
       </c>
       <c r="B3" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543116</v>
+        <v>543107</v>
       </c>
       <c r="R3" t="n">
-        <v>7209226</v>
+        <v>7209075</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120978039</v>
+        <v>120978034</v>
       </c>
       <c r="B4" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,34 +915,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543134</v>
+        <v>543114</v>
       </c>
       <c r="R4" t="n">
-        <v>7209039</v>
+        <v>7209229</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120978032</v>
+        <v>120978044</v>
       </c>
       <c r="B5" t="n">
-        <v>57351</v>
+        <v>78604</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,39 +1032,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543135</v>
+        <v>543123</v>
       </c>
       <c r="R5" t="n">
-        <v>7209257</v>
+        <v>7208937</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120978013</v>
+        <v>120978032</v>
       </c>
       <c r="B6" t="n">
-        <v>79717</v>
+        <v>57351</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,38 +1140,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>543076</v>
+        <v>543135</v>
       </c>
       <c r="R6" t="n">
-        <v>7209851</v>
+        <v>7209257</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,7 +1245,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120978051</v>
+        <v>120977997</v>
       </c>
       <c r="B7" t="n">
         <v>57351</v>
@@ -1285,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>543095</v>
+        <v>543057</v>
       </c>
       <c r="R7" t="n">
-        <v>7209049</v>
+        <v>7209403</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1320,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120978001</v>
+        <v>120978021</v>
       </c>
       <c r="B8" t="n">
-        <v>79683</v>
+        <v>91064</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1369,25 +1374,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>1506</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>543045</v>
+        <v>543115</v>
       </c>
       <c r="R8" t="n">
-        <v>7209613</v>
+        <v>7209734</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1432,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1447,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120978030</v>
+        <v>120978009</v>
       </c>
       <c r="B9" t="n">
-        <v>57504</v>
+        <v>79685</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,38 +1490,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>543137</v>
+        <v>543069</v>
       </c>
       <c r="R9" t="n">
-        <v>7209282</v>
+        <v>7209839</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1548,7 +1549,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1558,7 +1559,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,10 +1586,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120978022</v>
+        <v>120978004</v>
       </c>
       <c r="B10" t="n">
-        <v>90983</v>
+        <v>78604</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1601,21 +1602,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1625,10 +1626,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>543114</v>
+        <v>543044</v>
       </c>
       <c r="R10" t="n">
-        <v>7209734</v>
+        <v>7209633</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1660,7 +1661,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1670,7 +1671,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1697,10 +1698,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120978041</v>
+        <v>120978046</v>
       </c>
       <c r="B11" t="n">
-        <v>57351</v>
+        <v>78604</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1713,39 +1714,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>543164</v>
+        <v>543114</v>
       </c>
       <c r="R11" t="n">
-        <v>7208974</v>
+        <v>7208935</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1777,7 +1773,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1787,7 +1783,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1814,10 +1810,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120977997</v>
+        <v>120978024</v>
       </c>
       <c r="B12" t="n">
-        <v>57351</v>
+        <v>91102</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1830,39 +1826,29 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>543057</v>
+        <v>543114</v>
       </c>
       <c r="R12" t="n">
-        <v>7209403</v>
+        <v>7209731</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1894,7 +1880,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1904,7 +1890,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1931,10 +1917,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120978046</v>
+        <v>120978039</v>
       </c>
       <c r="B13" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1971,10 +1957,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>543114</v>
+        <v>543134</v>
       </c>
       <c r="R13" t="n">
-        <v>7208935</v>
+        <v>7209039</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2006,7 +1992,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2016,7 +2002,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2043,10 +2029,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120978025</v>
+        <v>120978000</v>
       </c>
       <c r="B14" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2059,34 +2045,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>543116</v>
+        <v>543043</v>
       </c>
       <c r="R14" t="n">
-        <v>7209729</v>
+        <v>7209590</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2118,7 +2109,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2128,7 +2119,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2155,10 +2146,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120978000</v>
+        <v>120978003</v>
       </c>
       <c r="B15" t="n">
-        <v>57351</v>
+        <v>82388</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2171,39 +2162,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>543043</v>
+        <v>543045</v>
       </c>
       <c r="R15" t="n">
-        <v>7209590</v>
+        <v>7209634</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2235,7 +2221,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2245,7 +2231,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2272,10 +2258,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120978042</v>
+        <v>120978027</v>
       </c>
       <c r="B16" t="n">
-        <v>57462</v>
+        <v>78604</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2284,42 +2270,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>543149</v>
+        <v>543112</v>
       </c>
       <c r="R16" t="n">
-        <v>7208877</v>
+        <v>7209467</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2351,7 +2333,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2361,7 +2343,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2388,10 +2370,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120978040</v>
+        <v>120978007</v>
       </c>
       <c r="B17" t="n">
-        <v>78601</v>
+        <v>79686</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2404,21 +2386,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2428,10 +2410,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>543164</v>
+        <v>543068</v>
       </c>
       <c r="R17" t="n">
-        <v>7208974</v>
+        <v>7209835</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2463,7 +2445,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2473,7 +2455,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2500,10 +2482,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120978043</v>
+        <v>120978037</v>
       </c>
       <c r="B18" t="n">
-        <v>57351</v>
+        <v>78604</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2516,39 +2498,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>543122</v>
+        <v>543124</v>
       </c>
       <c r="R18" t="n">
-        <v>7208939</v>
+        <v>7209053</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2580,7 +2557,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2590,7 +2567,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2617,10 +2594,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120978012</v>
+        <v>120978011</v>
       </c>
       <c r="B19" t="n">
-        <v>79718</v>
+        <v>79685</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2629,25 +2606,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2729,10 +2706,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120978007</v>
+        <v>120978043</v>
       </c>
       <c r="B20" t="n">
-        <v>79683</v>
+        <v>57351</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2745,34 +2722,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>543068</v>
+        <v>543122</v>
       </c>
       <c r="R20" t="n">
-        <v>7209835</v>
+        <v>7208939</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2804,7 +2786,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2814,7 +2796,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2841,10 +2823,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120978020</v>
+        <v>120978038</v>
       </c>
       <c r="B21" t="n">
-        <v>57462</v>
+        <v>57351</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2853,20 +2835,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2874,9 +2856,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2885,10 +2868,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>543115</v>
+        <v>543133</v>
       </c>
       <c r="R21" t="n">
-        <v>7209734</v>
+        <v>7209037</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2920,7 +2903,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2930,7 +2913,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2957,7 +2940,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120978055</v>
+        <v>120978045</v>
       </c>
       <c r="B22" t="n">
         <v>57351</v>
@@ -2993,7 +2976,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3002,10 +2985,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>543091</v>
+        <v>543114</v>
       </c>
       <c r="R22" t="n">
-        <v>7209093</v>
+        <v>7208935</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3037,7 +3020,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3047,7 +3030,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3074,10 +3057,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120978014</v>
+        <v>120978053</v>
       </c>
       <c r="B23" t="n">
-        <v>57351</v>
+        <v>91102</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3090,39 +3073,29 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>543091</v>
+        <v>543105</v>
       </c>
       <c r="R23" t="n">
-        <v>7209831</v>
+        <v>7209074</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3154,7 +3127,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3164,7 +3137,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3191,10 +3164,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120978009</v>
+        <v>120978013</v>
       </c>
       <c r="B24" t="n">
-        <v>79682</v>
+        <v>79720</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3203,25 +3176,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3231,10 +3204,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>543069</v>
+        <v>543076</v>
       </c>
       <c r="R24" t="n">
-        <v>7209839</v>
+        <v>7209851</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3266,7 +3239,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3276,7 +3249,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3303,10 +3276,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120978044</v>
+        <v>120978033</v>
       </c>
       <c r="B25" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3343,10 +3316,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>543123</v>
+        <v>543133</v>
       </c>
       <c r="R25" t="n">
-        <v>7208937</v>
+        <v>7209253</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3378,7 +3351,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3388,7 +3361,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3415,10 +3388,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120978027</v>
+        <v>120978056</v>
       </c>
       <c r="B26" t="n">
-        <v>78601</v>
+        <v>90727</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3431,21 +3404,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3455,10 +3428,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>543112</v>
+        <v>543091</v>
       </c>
       <c r="R26" t="n">
-        <v>7209467</v>
+        <v>7209092</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3490,7 +3463,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3500,7 +3473,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3527,10 +3500,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120978062</v>
+        <v>120978006</v>
       </c>
       <c r="B27" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3543,24 +3516,29 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
@@ -3570,7 +3548,7 @@
         <v>543075</v>
       </c>
       <c r="R27" t="n">
-        <v>7209164</v>
+        <v>7209798</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3602,7 +3580,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3612,7 +3590,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Påbörjat bohål</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3639,10 +3622,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120978050</v>
+        <v>120977996</v>
       </c>
       <c r="B28" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3655,34 +3638,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>543101</v>
+        <v>543049</v>
       </c>
       <c r="R28" t="n">
-        <v>7209025</v>
+        <v>7209349</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3714,7 +3702,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3724,7 +3712,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3751,10 +3739,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120978021</v>
+        <v>120977998</v>
       </c>
       <c r="B29" t="n">
-        <v>91052</v>
+        <v>57351</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3763,38 +3751,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1506</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>543115</v>
+        <v>543044</v>
       </c>
       <c r="R29" t="n">
-        <v>7209734</v>
+        <v>7209510</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3826,7 +3819,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3836,7 +3829,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3863,7 +3856,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120978028</v>
+        <v>120978051</v>
       </c>
       <c r="B30" t="n">
         <v>57351</v>
@@ -3899,7 +3892,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3908,10 +3901,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>543068</v>
+        <v>543095</v>
       </c>
       <c r="R30" t="n">
-        <v>7209436</v>
+        <v>7209049</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3943,7 +3936,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3953,7 +3946,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3980,10 +3973,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120978056</v>
+        <v>120978061</v>
       </c>
       <c r="B31" t="n">
-        <v>90715</v>
+        <v>74710</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3996,21 +3989,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4020,10 +4013,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>543091</v>
+        <v>543075</v>
       </c>
       <c r="R31" t="n">
-        <v>7209092</v>
+        <v>7209164</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4055,7 +4048,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4065,7 +4058,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4092,10 +4085,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120978063</v>
+        <v>120978050</v>
       </c>
       <c r="B32" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4132,10 +4125,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>543074</v>
+        <v>543101</v>
       </c>
       <c r="R32" t="n">
-        <v>7209182</v>
+        <v>7209025</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4167,7 +4160,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4177,7 +4170,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4204,10 +4197,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120978061</v>
+        <v>120978012</v>
       </c>
       <c r="B33" t="n">
-        <v>74708</v>
+        <v>79721</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4216,25 +4209,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>6464</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4244,10 +4237,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>543075</v>
+        <v>543072</v>
       </c>
       <c r="R33" t="n">
-        <v>7209164</v>
+        <v>7209851</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4279,7 +4272,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4289,7 +4282,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4316,10 +4309,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120978006</v>
+        <v>120978063</v>
       </c>
       <c r="B34" t="n">
-        <v>57351</v>
+        <v>78604</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4332,39 +4325,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>543075</v>
+        <v>543074</v>
       </c>
       <c r="R34" t="n">
-        <v>7209798</v>
+        <v>7209182</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4396,7 +4384,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4406,12 +4394,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:37</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Påbörjat bohål</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4438,10 +4421,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120977996</v>
+        <v>120978062</v>
       </c>
       <c r="B35" t="n">
-        <v>57351</v>
+        <v>78604</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4454,39 +4437,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>543049</v>
+        <v>543075</v>
       </c>
       <c r="R35" t="n">
-        <v>7209349</v>
+        <v>7209164</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4518,7 +4496,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4528,7 +4506,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4555,10 +4533,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120978052</v>
+        <v>120978040</v>
       </c>
       <c r="B36" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4595,10 +4573,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>543096</v>
+        <v>543164</v>
       </c>
       <c r="R36" t="n">
-        <v>7209059</v>
+        <v>7208974</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4630,7 +4608,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4640,7 +4618,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4667,10 +4645,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120978037</v>
+        <v>120978022</v>
       </c>
       <c r="B37" t="n">
-        <v>78601</v>
+        <v>90995</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4683,21 +4661,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4707,10 +4685,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>543124</v>
+        <v>543114</v>
       </c>
       <c r="R37" t="n">
-        <v>7209053</v>
+        <v>7209734</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4742,7 +4720,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4752,7 +4730,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4779,10 +4757,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120978060</v>
+        <v>120978008</v>
       </c>
       <c r="B38" t="n">
-        <v>77548</v>
+        <v>78604</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4795,21 +4773,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>314</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitskaftad svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenothecopsis viridialba</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Kremp.) A.F.W.Schmidt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4819,10 +4797,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>543079</v>
+        <v>543067</v>
       </c>
       <c r="R38" t="n">
-        <v>7209176</v>
+        <v>7209836</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4854,7 +4832,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4864,7 +4842,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4891,10 +4869,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120978053</v>
+        <v>120977999</v>
       </c>
       <c r="B39" t="n">
-        <v>91090</v>
+        <v>78604</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4907,16 +4885,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4926,10 +4909,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>543105</v>
+        <v>543048</v>
       </c>
       <c r="R39" t="n">
-        <v>7209074</v>
+        <v>7209511</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4961,7 +4944,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4971,7 +4954,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4998,10 +4981,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120978008</v>
+        <v>120978023</v>
       </c>
       <c r="B40" t="n">
-        <v>78601</v>
+        <v>90705</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5014,21 +4997,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5038,10 +5021,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>543067</v>
+        <v>543114</v>
       </c>
       <c r="R40" t="n">
-        <v>7209836</v>
+        <v>7209734</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5073,7 +5056,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5083,7 +5066,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5110,10 +5093,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120978016</v>
+        <v>120978026</v>
       </c>
       <c r="B41" t="n">
-        <v>79682</v>
+        <v>57351</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5126,34 +5109,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>543095</v>
+        <v>543114</v>
       </c>
       <c r="R41" t="n">
-        <v>7209831</v>
+        <v>7209471</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5185,7 +5173,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5195,7 +5183,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5222,10 +5210,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120978059</v>
+        <v>120978001</v>
       </c>
       <c r="B42" t="n">
-        <v>78601</v>
+        <v>79686</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5238,21 +5226,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5262,10 +5250,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>543087</v>
+        <v>543045</v>
       </c>
       <c r="R42" t="n">
-        <v>7209098</v>
+        <v>7209613</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5297,7 +5285,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5307,7 +5295,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5334,10 +5322,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120978048</v>
+        <v>120978060</v>
       </c>
       <c r="B43" t="n">
-        <v>78601</v>
+        <v>77551</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5350,21 +5338,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitskaftad svartspik</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis viridialba</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kremp.) A.F.W.Schmidt</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5374,10 +5362,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>543107</v>
+        <v>543079</v>
       </c>
       <c r="R43" t="n">
-        <v>7209000</v>
+        <v>7209176</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5409,7 +5397,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5419,7 +5407,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5446,10 +5434,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120978002</v>
+        <v>120978016</v>
       </c>
       <c r="B44" t="n">
-        <v>78601</v>
+        <v>79685</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5462,21 +5450,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5486,10 +5474,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>543045</v>
+        <v>543095</v>
       </c>
       <c r="R44" t="n">
-        <v>7209613</v>
+        <v>7209831</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5521,7 +5509,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5531,7 +5519,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5558,10 +5546,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120978019</v>
+        <v>120978015</v>
       </c>
       <c r="B45" t="n">
-        <v>79711</v>
+        <v>78604</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5570,25 +5558,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5598,10 +5586,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>543161</v>
+        <v>543086</v>
       </c>
       <c r="R45" t="n">
-        <v>7209834</v>
+        <v>7209826</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5633,7 +5621,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5643,7 +5631,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5670,10 +5658,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120978054</v>
+        <v>120978036</v>
       </c>
       <c r="B46" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5686,34 +5674,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>543107</v>
+        <v>543123</v>
       </c>
       <c r="R46" t="n">
-        <v>7209075</v>
+        <v>7209054</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5745,7 +5738,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5755,7 +5748,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5782,7 +5775,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120978036</v>
+        <v>120978005</v>
       </c>
       <c r="B47" t="n">
         <v>57351</v>
@@ -5818,7 +5811,7 @@
       <c r="I47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5827,10 +5820,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>543123</v>
+        <v>543049</v>
       </c>
       <c r="R47" t="n">
-        <v>7209054</v>
+        <v>7209680</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5862,7 +5855,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5872,7 +5865,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5899,10 +5892,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120978034</v>
+        <v>120978020</v>
       </c>
       <c r="B48" t="n">
-        <v>57351</v>
+        <v>57462</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5911,20 +5904,20 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5932,10 +5925,9 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5944,10 +5936,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>543114</v>
+        <v>543115</v>
       </c>
       <c r="R48" t="n">
-        <v>7209229</v>
+        <v>7209734</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5979,7 +5971,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5989,7 +5981,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6016,10 +6008,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120978003</v>
+        <v>120978028</v>
       </c>
       <c r="B49" t="n">
-        <v>82385</v>
+        <v>57351</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6032,34 +6024,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>543045</v>
+        <v>543068</v>
       </c>
       <c r="R49" t="n">
-        <v>7209634</v>
+        <v>7209436</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6091,7 +6088,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6101,7 +6098,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6128,10 +6125,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120977999</v>
+        <v>120978052</v>
       </c>
       <c r="B50" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6168,10 +6165,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>543048</v>
+        <v>543096</v>
       </c>
       <c r="R50" t="n">
-        <v>7209511</v>
+        <v>7209059</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6203,7 +6200,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6213,7 +6210,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6240,10 +6237,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120978018</v>
+        <v>120978019</v>
       </c>
       <c r="B51" t="n">
-        <v>79711</v>
+        <v>79714</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6280,10 +6277,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>543095</v>
+        <v>543161</v>
       </c>
       <c r="R51" t="n">
-        <v>7209831</v>
+        <v>7209834</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6315,7 +6312,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6325,7 +6322,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6352,10 +6349,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120978010</v>
+        <v>120978018</v>
       </c>
       <c r="B52" t="n">
-        <v>79711</v>
+        <v>79714</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6392,10 +6389,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>543067</v>
+        <v>543095</v>
       </c>
       <c r="R52" t="n">
-        <v>7209836</v>
+        <v>7209831</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6427,7 +6424,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6437,7 +6434,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6464,10 +6461,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120978038</v>
+        <v>120978035</v>
       </c>
       <c r="B53" t="n">
-        <v>57351</v>
+        <v>78604</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6480,39 +6477,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>543133</v>
+        <v>543116</v>
       </c>
       <c r="R53" t="n">
-        <v>7209037</v>
+        <v>7209226</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6544,7 +6536,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6554,7 +6546,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6581,10 +6573,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120977998</v>
+        <v>120978025</v>
       </c>
       <c r="B54" t="n">
-        <v>57351</v>
+        <v>78604</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6597,39 +6589,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>543044</v>
+        <v>543116</v>
       </c>
       <c r="R54" t="n">
-        <v>7209510</v>
+        <v>7209729</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6661,7 +6648,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6671,7 +6658,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6698,10 +6685,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120978045</v>
+        <v>120978029</v>
       </c>
       <c r="B55" t="n">
-        <v>57351</v>
+        <v>78604</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6714,39 +6701,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>543114</v>
+        <v>543068</v>
       </c>
       <c r="R55" t="n">
-        <v>7208935</v>
+        <v>7209436</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6778,7 +6760,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6788,7 +6770,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6815,10 +6797,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120978047</v>
+        <v>120978030</v>
       </c>
       <c r="B56" t="n">
-        <v>90693</v>
+        <v>57504</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6831,34 +6813,38 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>543105</v>
+        <v>543137</v>
       </c>
       <c r="R56" t="n">
-        <v>7209001</v>
+        <v>7209282</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6890,7 +6876,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6900,7 +6886,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6927,10 +6913,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120978033</v>
+        <v>120978014</v>
       </c>
       <c r="B57" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6943,34 +6929,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>543133</v>
+        <v>543091</v>
       </c>
       <c r="R57" t="n">
-        <v>7209253</v>
+        <v>7209831</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -7002,7 +6993,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7012,7 +7003,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7039,10 +7030,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120978011</v>
+        <v>120978042</v>
       </c>
       <c r="B58" t="n">
-        <v>79682</v>
+        <v>57462</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7051,38 +7042,42 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>103031</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>543072</v>
+        <v>543149</v>
       </c>
       <c r="R58" t="n">
-        <v>7209851</v>
+        <v>7208877</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7114,7 +7109,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7124,7 +7119,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7151,10 +7146,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120978026</v>
+        <v>120978059</v>
       </c>
       <c r="B59" t="n">
-        <v>57351</v>
+        <v>78604</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7167,39 +7162,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>543114</v>
+        <v>543087</v>
       </c>
       <c r="R59" t="n">
-        <v>7209471</v>
+        <v>7209098</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7231,7 +7221,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7241,7 +7231,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7268,7 +7258,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120978005</v>
+        <v>120978055</v>
       </c>
       <c r="B60" t="n">
         <v>57351</v>
@@ -7313,10 +7303,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>543049</v>
+        <v>543091</v>
       </c>
       <c r="R60" t="n">
-        <v>7209680</v>
+        <v>7209093</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7348,7 +7338,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7358,7 +7348,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7385,10 +7375,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120978049</v>
+        <v>120978017</v>
       </c>
       <c r="B61" t="n">
-        <v>90693</v>
+        <v>79686</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7401,21 +7391,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7425,10 +7415,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>543099</v>
+        <v>543095</v>
       </c>
       <c r="R61" t="n">
-        <v>7209028</v>
+        <v>7209831</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7460,7 +7450,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7470,7 +7460,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7497,10 +7487,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120978017</v>
+        <v>120978049</v>
       </c>
       <c r="B62" t="n">
-        <v>79683</v>
+        <v>90705</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7513,21 +7503,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7537,10 +7527,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>543095</v>
+        <v>543099</v>
       </c>
       <c r="R62" t="n">
-        <v>7209831</v>
+        <v>7209028</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7572,7 +7562,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7582,7 +7572,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7609,10 +7599,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120978029</v>
+        <v>120978010</v>
       </c>
       <c r="B63" t="n">
-        <v>78601</v>
+        <v>79714</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7621,25 +7611,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7649,10 +7639,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>543068</v>
+        <v>543067</v>
       </c>
       <c r="R63" t="n">
-        <v>7209436</v>
+        <v>7209836</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7684,7 +7674,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7694,7 +7684,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7721,10 +7711,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120978031</v>
+        <v>120978047</v>
       </c>
       <c r="B64" t="n">
-        <v>78601</v>
+        <v>90705</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7737,21 +7727,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7761,10 +7751,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>543135</v>
+        <v>543105</v>
       </c>
       <c r="R64" t="n">
-        <v>7209283</v>
+        <v>7209001</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7796,7 +7786,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7806,7 +7796,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7833,10 +7823,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120978024</v>
+        <v>120978048</v>
       </c>
       <c r="B65" t="n">
-        <v>91090</v>
+        <v>78604</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7849,16 +7839,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7868,10 +7863,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>543114</v>
+        <v>543107</v>
       </c>
       <c r="R65" t="n">
-        <v>7209731</v>
+        <v>7209000</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7903,7 +7898,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7913,7 +7908,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7940,10 +7935,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120978023</v>
+        <v>120978002</v>
       </c>
       <c r="B66" t="n">
-        <v>90693</v>
+        <v>78604</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7956,21 +7951,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7980,10 +7975,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>543114</v>
+        <v>543045</v>
       </c>
       <c r="R66" t="n">
-        <v>7209734</v>
+        <v>7209613</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -8015,7 +8010,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8025,7 +8020,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8052,10 +8047,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120978004</v>
+        <v>120978041</v>
       </c>
       <c r="B67" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8068,34 +8063,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Rödingsjöbäcken, Ås lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>543044</v>
+        <v>543164</v>
       </c>
       <c r="R67" t="n">
-        <v>7209633</v>
+        <v>7208974</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -8127,7 +8127,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8137,7 +8137,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD67" t="b">
